--- a/output/variaveis_indicadores.xlsx
+++ b/output/variaveis_indicadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.barbosa\Desktop\Repositorios\PNADC-Piaui-desagregada\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D85A13-BEB7-4D88-96CA-2A41FB5B60CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9DCED9-838B-40B6-A245-806FE6BDF43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1905" windowWidth="27810" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="495" yWindow="1635" windowWidth="27810" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
   <si>
     <t>Dimensão</t>
   </si>
@@ -67,63 +67,18 @@
     <t>Média (R$ reais)</t>
   </si>
   <si>
-    <t>Rendimento_Medio_Habitual</t>
-  </si>
-  <si>
-    <t>Rendimento_Formal</t>
-  </si>
-  <si>
-    <t>Rendimento_Informal</t>
-  </si>
-  <si>
     <t>Razão</t>
   </si>
   <si>
-    <t>Desigualdade_Formal_Informal</t>
-  </si>
-  <si>
     <t>Índice (0–1)</t>
   </si>
   <si>
-    <t>Gini_Rendimento_Habitual_Trabalho</t>
-  </si>
-  <si>
     <t>Vulnerabilidade</t>
   </si>
   <si>
-    <t>Desalentados_Forca_Ampliada</t>
-  </si>
-  <si>
-    <t>Desalentados_Fora_Forca</t>
-  </si>
-  <si>
     <t>Distribuição (%)</t>
   </si>
   <si>
-    <t>Motivo_Desistencia_Desalentado</t>
-  </si>
-  <si>
-    <t>Taxa_Nem_Nem</t>
-  </si>
-  <si>
-    <t>Motivo_Nao_Procura_NemNem</t>
-  </si>
-  <si>
-    <t>Perfil da população em idade para trabalhar</t>
-  </si>
-  <si>
-    <t>Distribuicao_PIT_por_Sexo</t>
-  </si>
-  <si>
-    <t>Distribuicao_PIT_por_Raca</t>
-  </si>
-  <si>
-    <t>Distribuicao_PIT_por_Faixa_Etaria_SIDRA</t>
-  </si>
-  <si>
-    <t>Distribuicao_PIT_por_Instrucao_SIDRA</t>
-  </si>
-  <si>
     <t>Composição das pessoas em idade de trabalhar por nível de instrução (VD3004). Só no recorte Total</t>
   </si>
   <si>
@@ -163,12 +118,6 @@
     <t>Ocupados com ensino médio completo ou mais ÷ ocupados</t>
   </si>
   <si>
-    <t>Empregados do setor privado com e sem carteira, sem contar os domésticos.</t>
-  </si>
-  <si>
-    <t>Empregados do setor público com e sem carteira, mais militares e estatutários.</t>
-  </si>
-  <si>
     <t>Rendimento habitual de todos os trabalhos, deflacionado</t>
   </si>
   <si>
@@ -190,12 +139,6 @@
     <t>Desalentados ÷ força de trabalho potencial</t>
   </si>
   <si>
-    <t>Motivo de não ter procurado trabalho, agrupado em "não havia trabalho na localidade" e "outros". Só Brasil, Nordeste e Piauí, recorte Total</t>
-  </si>
-  <si>
-    <t>Motivo de não procurar trabalho, agrupado em afazeres/cuidados, saúde/gravidez e outros. Só Brasil, Nordeste e Piauí, recorte Total</t>
-  </si>
-  <si>
     <t>Rendimento habitual real dos ocupados formais</t>
   </si>
   <si>
@@ -211,18 +154,6 @@
     <t xml:space="preserve">Composição das pessoas em idade de trabalhar por faixa etária: 14–17, 18–24, 25–39, 40–59, 60+ </t>
   </si>
   <si>
-    <t>Taxa de Participacao</t>
-  </si>
-  <si>
-    <t>Nivel de Ocupacao</t>
-  </si>
-  <si>
-    <t>Taxa de Desocupacao</t>
-  </si>
-  <si>
-    <t>Taxa Composta de Subutilizacao</t>
-  </si>
-  <si>
     <t>Chefes de Familia Desocupados</t>
   </si>
   <si>
@@ -260,13 +191,88 @@
   </si>
   <si>
     <t>Ocupados na Agropecuária</t>
+  </si>
+  <si>
+    <t>Rendimento Médio Habitual</t>
+  </si>
+  <si>
+    <t>Rendimento Formal</t>
+  </si>
+  <si>
+    <t>Rendimento Informal</t>
+  </si>
+  <si>
+    <t>Desigualdade de rendimentos entres Formal e Informal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indice de Gini do rendimento habitual nominal </t>
+  </si>
+  <si>
+    <t>Desalentados na Forca de trabalho Ampliada</t>
+  </si>
+  <si>
+    <t>Taxa de jovens Nem e Nem</t>
+  </si>
+  <si>
+    <t>Desalentados Fora da Força de trabalho</t>
+  </si>
+  <si>
+    <t>Motivo de não procurar trabalho, agrupado em afazeres/cuidados, saúde/gravidez e outros. Só Brasil, Nordeste e Piauí</t>
+  </si>
+  <si>
+    <t>Motivo de não ter procurado trabalho, agrupado em "não havia trabalho na localidade" e "outros". Só Brasil, Nordeste e Piauí</t>
+  </si>
+  <si>
+    <t>Motivo de Desistência dos Desalentados</t>
+  </si>
+  <si>
+    <t>Motivo de Não Procurar trabalho dos jovens Nem e Nem</t>
+  </si>
+  <si>
+    <t>Perfil da população em idade para trabalhar (PIT)</t>
+  </si>
+  <si>
+    <t>Distribuição da PIT por Sexo</t>
+  </si>
+  <si>
+    <t>Distribuição da PIT por Raça</t>
+  </si>
+  <si>
+    <t>Distribuição da PIT por Faixa Etária</t>
+  </si>
+  <si>
+    <t>Distribuição da PIT por nível de instrução</t>
+  </si>
+  <si>
+    <t>Taxa de Participação</t>
+  </si>
+  <si>
+    <t>Nivel de Ocupação</t>
+  </si>
+  <si>
+    <t>Taxa de Desocupação</t>
+  </si>
+  <si>
+    <t>Taxa Composta de Subutilização</t>
+  </si>
+  <si>
+    <t>Empregados do setor privado com e sem carteira, sem contar os domésticos</t>
+  </si>
+  <si>
+    <t>Empregados do setor público com e sem carteira, mais militares e estatutários</t>
+  </si>
+  <si>
+    <t>Pessoas que estavam trabalhando na semana de referência</t>
+  </si>
+  <si>
+    <t>Pessoas que não estavam trabalhando mas dispostas a trabalhar e procuraram emprego na semana de referência</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +288,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -291,7 +312,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -299,20 +320,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,390 +700,390 @@
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="144.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s">
+      <c r="D27" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D31" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s">
+      <c r="D32" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D33" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D34" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="D24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1060,5 +1105,6 @@
     <mergeCell ref="B16:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/output/variaveis_indicadores.xlsx
+++ b/output/variaveis_indicadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.barbosa\Desktop\Repositorios\PNADC-Piaui-desagregada\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9DCED9-838B-40B6-A245-806FE6BDF43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6A3BE3-1AF9-4B4F-A4C3-D8D6E8093F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="1635" windowWidth="27810" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12945" yWindow="4095" windowWidth="27810" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="1" r:id="rId1"/>
@@ -58,9 +58,6 @@
     <t>Total (pessoas)</t>
   </si>
   <si>
-    <t>Qualidade da ocupação</t>
-  </si>
-  <si>
     <t>Rendimento e desigualdade</t>
   </si>
   <si>
@@ -266,6 +263,9 @@
   </si>
   <si>
     <t>Pessoas que não estavam trabalhando mas dispostas a trabalhar e procuraram emprego na semana de referência</t>
+  </si>
+  <si>
+    <t>Inserção no mercado de trabalho</t>
   </si>
 </sst>
 </file>
@@ -354,10 +354,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,388 +721,388 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="B31:B34"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
